--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.4228442658341</v>
+        <v>3.318712193198041</v>
       </c>
       <c r="D2" t="n">
-        <v>20.16318475188443</v>
+        <v>3.27651752218122</v>
       </c>
       <c r="E2" t="n">
-        <v>3.147291815810977</v>
+        <v>0.511434920069284</v>
       </c>
       <c r="F2" t="n">
-        <v>2.521005475613016</v>
+        <v>0.4096633897871154</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.71742789745605</v>
+        <v>4.341582033336609</v>
       </c>
       <c r="D3" t="n">
-        <v>25.20519570311046</v>
+        <v>4.09584430175545</v>
       </c>
       <c r="E3" t="n">
-        <v>3.147291815810977</v>
+        <v>0.511434920069284</v>
       </c>
       <c r="F3" t="n">
-        <v>2.521005475613016</v>
+        <v>0.4096633897871154</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
